--- a/PTBR/Lang/PTBR/Game/Zone.xlsx
+++ b/PTBR/Lang/PTBR/Game/Zone.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -679,7 +679,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Você vê Port Kapul. O porto está cheio de mercadores.</t>
+          <t>Você vê Porto Kapul. O porto está repleto de mercadores.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>O Grande Glaciar</t>
+          <t>A Grande Geleira</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Um lugar outrora repleto de vida. Foi um dos Jardins de Elin.</t>
+          <t xml:space="preserve">Um lugar outrora cheio de vida. Era um dos Jardins de Elin.  </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vista Agradável</t>
+          <t>Pleasantview</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Selvagens</t>
+          <t>Ermos</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>O hospital gratuito para onde os gravemente feridos são enviados.</t>
+          <t>O hospital gratuito para onde os gravemente feridos são levados.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Selvagens</t>
+          <t>Ermos</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Um lugar desconhecido onde criaturas desconhecidas e pessoas desaparecidas vagueiam.</t>
+          <t>Um lugar desconhecido onde criaturas estranhas e desaparecidos vagueiam.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sala de Desenvolvimento</t>
+          <t>Sala de Dev</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Exterior da Sala de Desenvolvimento</t>
+          <t>Exterior da Sala de Dev</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pequena Caverna</t>
+          <t>Caverna Pequena</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Prado</t>
+          <t>Campina</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Você vê as ruínas de Lysanas. Você sente que algo importante está adormecido lá.</t>
+          <t>Você vê as ruínas de Lysanas. Você sente que algo importante dorme ali.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Que lugar é este...?</t>
+          <t>Que lugar é esse...?</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cratera Mais Luminosa</t>
+          <t>Cratera de Lumiest</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Acampamento do Artífice</t>
+          <t>Acampamento dos Latoeiros</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Você vê um acampamento de artífices itinerantes. Está tão animado quanto um canto da cidade!</t>
+          <t>Você vê um acampamento de latoeiros itinerantes. Tão animado quanto um quarteirão de cidade!</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Você vê a cidade de Olvina. O aroma de vinho e de águas termais preenche o ar.</t>
+          <t>Você vê a cidade de Olvina. O cheiro de vinho e águas termais enche o ar.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Você vê a embaixada de Palmia. O prédio está fortemente protegido.</t>
+          <t>Você vê a embaixada de Palmia. O prédio é fortemente guardado.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Você vê um edifício muito estranho.</t>
+          <t>Você vê um prédio muito estranho.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Você vê uma pequena cidade, Yowyn. Você se lembra com carinho do cheiro do solo.</t>
+          <t>Você vê uma pequena cidade, Yowyn. Você lembra com carinho do cheiro de terra.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Você vê uma árvore enorme. Fadas dançam graciosamente ao seu redor.</t>
+          <t>Você vê uma árvore enorme. Fadas dançam graciosamente ao redor dela.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Você vê uma aldeia abandonada na floresta sombria.</t>
+          <t>Você vê uma vila abandonada na floresta escura.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Aldeia Mifu</t>
+          <t>Vila Mifu</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Você vê uma vila pacífica. O cheiro de arroz está no ar.</t>
+          <t>Você vê uma vila pacífica. O cheiro de arroz paira no ar.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Aldeia Nefu</t>
+          <t>Vila Nefu</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Você vê um templo grande e exótico. O som de uma cachoeira ressoa.</t>
+          <t>Você vê um templo grande e exótico. O som da cachoeira ressoa.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Você vê um dirigível imenso flutuando no céu.</t>
+          <t>Você vê uma aeronave colossal flutuando no céu.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Você vê a grande cidade de Palmia. A cidade inteira está cercada por um alto muro.</t>
+          <t>Você vê a grande cidade de Palmia. A cidade inteira é cercada por muralhas altas.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>You see the great city of Palmia. Entire city is surrounded by tall wall.</t>
+          <t>You see the great city of Palmia. Entire city is surrounded by tall walls.</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Você vê um elegante castelo. Os salgueiros balançam ao vento.</t>
+          <t>Você vê uma fortaleza elegante. Os salgueiros balançam ao vento.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Você vê a cidade de Mysilia. Cercada pela natureza, a cidade parece calma e tranquila.</t>
+          <t>Você vê a cidade de Mysilia. Cercada pela natureza, a cidade transmite calma e paz.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Você vê o infame covil do fora-da-lei Derphy.</t>
+          <t>Você vê o famoso covil de ladrões, Derphy.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Covil das Meretrizes de Derphy</t>
+          <t>Bordel de Derphy</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Caverna do Filhote</t>
+          <t>Caverna do Cachorrinho</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cadeia</t>
+          <t>Prisão</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Antigo Castelo</t>
+          <t>Torre Antiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2388,109 +2388,109 @@
       <c r="E56" t="inlineStr">
         <is>
           <t>古城</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Você vê um castelo belo e desgastado pelo tempo. Você não consegue deixar de ser atraído por ele.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>You see a weathered, beautiful castle. You cannot help but feel drawn to it.</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>古びた美しい城が見える。不思議と心を引かれる。</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>oldchurch</t>
+          <t>oldkeep_dungeon</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EA 23.274</t>
+          <t>EA 23.344</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Igreja Antiga</t>
+          <t>Torre Antiga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Old Church</t>
+          <t>Old Keep</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>古い教会</t>
+          <t>古城</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>keep_seeker</t>
+          <t>oldchurch</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Alpha 20.64</t>
+          <t>EA 23.274</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Castelo do Buscador</t>
+          <t>Igreja Velha</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Seeker's Keep</t>
+          <t>Old Church</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>探求者の孤城</t>
+          <t>古い教会</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cave_dead</t>
+          <t>keep_seeker</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 20.64</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cripta dos Condenados</t>
+          <t>Fortaleza do Buscador</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Crypt of the Damned</t>
+          <t>Seeker's Keep</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>死者の洞窟</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>Um calafrio gelado percorreu seu corpo, congelando-o de dentro para fora.</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>A cold shiver ran through you, freezing you from the inside out.</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>体の芯まで凍りつくような寒気を感じる。</t>
+          <t>探求者の孤城</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>cave_lerna</t>
+          <t>cave_dead</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2500,24 +2500,39 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Passagem Montanhosa</t>
+          <t>Cripta dos Condenados</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Mountain Pass</t>
+          <t>Crypt of the Damned</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>山道への入り口</t>
+          <t>死者の洞窟</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Um arrepio frio percorre você, congelando você por dentro.</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>A cold shiver ran through you, freezing you from the inside out.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>体の芯まで凍りつくような寒気を感じる。</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>larna</t>
+          <t>cave_lerna</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2527,24 +2542,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Larna</t>
+          <t>Passo da Montanha</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Larna</t>
+          <t>Mountain Pass</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ラーナ</t>
+          <t>山道への入り口</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>housedome</t>
+          <t>larna</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2554,108 +2569,93 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Domo da Casa</t>
+          <t>Larna</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>House Dome</t>
+          <t>Larna</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ハウスドーム</t>
+          <t>ラーナ</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>little_garden</t>
+          <t>housedome</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Alpha 20.65</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jardim Pequeno</t>
+          <t>Domo Residencial</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Little Garden</t>
+          <t>House Dome</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>リトルガーデン</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Você vê um jardim bem cuidado. Ele lhe transmite uma sensação acolhedora.</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>You see a well-maintained garden. It gives you a warm feeling inside.</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>綺麗に手入れされた庭が見える。心が温まる感じがする。</t>
+          <t>ハウスドーム</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>chaos_castle</t>
+          <t>little_garden</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 20.65</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fortaleza do Caos</t>
+          <t>Pequeno Jardim</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Fort of Chaos</t>
+          <t>Little Garden</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>不気味な城</t>
+          <t>リトルガーデン</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Você vê um forte de outro mundo. Sua voz interior te adverte para não ir lá.</t>
+          <t>Você vê um jardim bem cuidado. Ele aquece você por dentro.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>You see an unearthly fort. Your inner voice wanrs you to not go there.</t>
+          <t>You see a well-maintained garden. It gives you a warm feeling inside.</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>不気味な城がある。絶対に入ってはいけない予感がする。</t>
+          <t>綺麗に手入れされた庭が見える。心が温まる感じがする。</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>cave_mino</t>
+          <t>chaos_castle</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2665,39 +2665,39 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ninho do Minotauro</t>
+          <t>Forte do Caos</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Minotaur's Nest</t>
+          <t>Fort of Chaos</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ミノタウロスの巣</t>
+          <t>不気味な城</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>É o covil de um minotauro. O buraco de entrada é enorme.</t>
+          <t>Você vê um forte sobrenatural. Sua voz interior avisa para não ir até lá.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>It’s a minotaur’s lair. The entrance hole is enormous.</t>
+          <t>You see an unearthly fort. Your inner voice warns you to not go there.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>ミノタウロスの巣だ。入口の穴はとても大きい。</t>
+          <t>不気味な城がある。絶対に入ってはいけない予感がする。</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>cave_yeek</t>
+          <t>cave_mino</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2707,150 +2707,150 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Caverna dos Yeek</t>
+          <t>Ninho do Minotauro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Yeek Cave</t>
+          <t>Minotaur's Nest</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>イークの洞窟</t>
+          <t>ミノタウロスの巣</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Você vê uma caverna habitada por yeeks. A entrada não passa de um buraco.</t>
+          <t>É o covil de um minotauro. O buraco de entrada é enorme.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>You see a cave inhabited by yeeks. The entrance is scarcely more than a hole.</t>
+          <t>It’s a minotaur’s lair. The entrance hole is enormous.</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>イークが住む洞窟だ。入口の穴はとても小さい。</t>
+          <t>ミノタウロスの巣だ。入口の穴はとても大きい。</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>cave_fairy</t>
+          <t>cave_yeek</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EA 23.184</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Floresta do Caminho Perdido</t>
+          <t>Caverna dos Yeeks</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Forest of the Lost Way</t>
+          <t>Yeek Cave</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>帰らずの森</t>
+          <t>イークの洞窟</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Você vê uma caverna habitada por yeeks. A entrada é pouco mais que um buraco.</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>You see a cave inhabited by yeeks. The entrance is scarcely more than a hole.</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>イークが住む洞窟だ。入口の穴はとても小さい。</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>temple_undersea</t>
+          <t>cave_fairy</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EA 23.133</t>
+          <t>EA 23.184</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Templo Submerso de Lurie</t>
+          <t>Floresta do Caminho Perdido</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sunken Temple of Lurie</t>
+          <t>Forest of the Lost Way</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ルーリエ海底神殿</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Você vê uma entrada que leva às ruínas submersas sob o mar.</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>You see an entrance leading to the ruins sunken beneath the sea.</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>海底に沈んだ遺跡への入口がある。</t>
+          <t>帰らずの森</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>lumiest</t>
+          <t>temple_undersea</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.133</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Mais Luminoso</t>
+          <t>Templo Submerso de Lurie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Lumiest</t>
+          <t>Sunken Temple of Lurie</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ルミエスト</t>
+          <t>ルーリエ海底神殿</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Você vê Lumiest. O murmúrio da água ecoa agradavelmente.</t>
+          <t>Você vê uma entrada que leva às ruínas submersas sob o mar.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>You see Lumiest. Murmuring of water pleasantly echos.</t>
+          <t>You see an entrance leading to the ruins sunken beneath the sea.</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>ルミエストの都が見える。水のせせらぎが聴こえる。</t>
+          <t>海底に沈んだ遺跡への入口がある。</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>truce_ground</t>
+          <t>lumiest</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2860,66 +2860,81 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Terra da Trégua</t>
+          <t>Lumiest</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Truce Ground</t>
+          <t>Lumiest</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>神々の休戦地</t>
+          <t>ルミエスト</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Você vê antigos santuários. Um ar sagrado envolve o chão.</t>
+          <t>Você vê Lumiest. O murmúrio das águas ecoa agradavelmente.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>You see old shrines. Sacred air surrounds the ground.</t>
+          <t>You see Lumiest. Murmuring of water pleasantly echos.</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>寺院がある。神聖な雰囲気がする。</t>
+          <t>ルミエストの都が見える。水のせせらぎが聴こえる。</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>curryruin</t>
+          <t>truce_ground</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EA 23.190</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Acampamento das Ruínas Doga</t>
+          <t>Campo da Trégua</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Doga Ruins Camp</t>
+          <t>Truce Ground</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ドーガ遺跡キャンプ</t>
+          <t>神々の休戦地</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Você vê santuários antigos. Um ar sagrado envolve o terreno.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>You see old shrines. Sacred air surrounds the ground.</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>寺院がある。神聖な雰囲気がする。</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>curryruin_dungeon</t>
+          <t>curryruin</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2929,177 +2944,147 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fábrica de Doga</t>
+          <t>Acampamento das Ruínas de Doga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Factory of Doga</t>
+          <t>Doga Ruins Camp</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ドーガの工場</t>
+          <t>ドーガ遺跡キャンプ</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>miral_garok</t>
+          <t>academy_roran</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.348</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Oficina de Miral e Garokk</t>
+          <t>Academia de Roran</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Miral and Garokk's Workshop</t>
+          <t>Roran Academy</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>工房ミラル・ガロク</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Você vê um pequeno e pitoresco ateliê. Os sons de gatos miando alcançam seus ouvidos.</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>You see a quaint little workshop. The sounds of cats meowing reach your ears.</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>こじんまりとした工房がある。猫の鳴き声が聞こえる。</t>
+          <t>ローラン女学院</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>house_sister</t>
+          <t>curryruin_dungeon</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.190</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>A Mansão da Irmã Mais Nova</t>
+          <t>Fábrica de Doga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>The Mansion of Younger Sister</t>
+          <t>Factory of Doga</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>妹の館</t>
+          <t>ドーガの工場</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>guild_merchant</t>
+          <t>miral_garok</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Alpha 12.1</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Guilda dos Mercadores</t>
+          <t>Oficina de Miral e Garokk</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Merchants Guild</t>
+          <t>Miral and Garokk's Workshop</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>商人ギルド</t>
+          <t>工房ミラル・ガロク</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Você vê uma guilda de mercadores. Numerosas carroças estão estacionadas por perto.</t>
+          <t>Você vê uma pequena oficina pitoresca. Miados de gatos chegam aos seus ouvidos.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>You see a merchants guild. Numerous carts are parked nearby.</t>
+          <t>You see a quaint little workshop. The sounds of cats meowing reach your ears.</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>商人ギルドがある。たくさんの荷車が停めてある。</t>
+          <t>こじんまりとした工房がある。猫の鳴き声が聞こえる。</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>cursed_manor</t>
+          <t>house_sister</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Alpha 12.1</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>A Mansão Amaldiçoada</t>
+          <t>A Mansão da Irmãzinha</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>The Cursed Manor</t>
+          <t>The Mansion of Younger Sister</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>呪われた館</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Você vê uma grandiosa mansão. O ar ao redor parece muito frio.</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>You see a grand mansion. The air around feels very cold.</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>大きなお屋敷が見える。辺りの空気はとても冷たい。</t>
+          <t>妹の館</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>cursed_manor_dungeon</t>
+          <t>guild_merchant</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3109,219 +3094,234 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>A Mansão Amaldiçoada</t>
+          <t>Guilda dos Mercadores</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>The Cursed Manor</t>
+          <t>Merchants Guild</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>呪われた館</t>
+          <t>商人ギルド</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Você vê uma guilda de mercadores. Numerosos carrinhos estão estacionados por perto.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>You see a merchants guild. Numerous carts are parked nearby.</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>商人ギルドがある。たくさんの荷車が停めてある。</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>noyel</t>
+          <t>cursed_manor</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 12.1</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Noyel</t>
+          <t>A Mansão Amaldiçoada</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Noyel</t>
+          <t>The Cursed Manor</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ノイエル</t>
+          <t>呪われた館</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Você vê Noyel. As risadas das crianças ecoam do parquinho.</t>
+          <t>Você vê uma mansão imponente. O ar ao redor parece muito frio.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>You see Noyel. The laughters of children travel from the playground.</t>
+          <t>You see a grand mansion. The air around feels very cold.</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>ノイエルの村がある。子供たちの笑い声が聞こえる。</t>
+          <t>大きなお屋敷が見える。辺りの空気はとても冷たい。</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>windrest</t>
+          <t>cursed_manor_dungeon</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Alpha 13.1</t>
+          <t>Alpha 12.1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>O Lugar Onde os Ventos Descansam</t>
+          <t>A Mansão Amaldiçoada</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Where Winds Rest</t>
+          <t>The Cursed Manor</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>風の眠る場所</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Você vê uma floresta completamente imóvel, sem um único sopro de vento.</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>You see a forest utterly still, without a single breath of wind.</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>見慣れない木々がそびえ立っている。風一つ吹いていない静かな森だ。</t>
+          <t>呪われた館</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>snowgrave</t>
+          <t>noyel</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Alpha 14.1</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Permafrost</t>
+          <t>Noyel</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Permafrost</t>
+          <t>Noyel</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>永久凍土</t>
+          <t>ノイエル</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Será que este é... o fim do mundo?</t>
+          <t>Você vê Noyel. Os risos das crianças chegam do parquinho.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Is this... the end of the world?</t>
+          <t>You see Noyel. The laughters of children travel from the playground.</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>ここは…世界の果てだろうか？</t>
+          <t>ノイエルの村がある。子供たちの笑い声が聞こえる。</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>lumiest_graveyard</t>
+          <t>windrest</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 13.1</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>O Cemitério</t>
+          <t>Onde os Ventos Descansam</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>The Graveyard</t>
+          <t>Where Winds Rest</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>墓所</t>
+          <t>風の眠る場所</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Você vê o cemitério de Lumiest. Está silencioso. Muito silencioso.</t>
+          <t>Você vê uma floresta completamente imóvel, sem um único sopro de vento.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>You see the graveyard of Lumiest. It's slient. Very silent.</t>
+          <t>You see a forest utterly still, without a single breath of wind.</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>墓所が見える。辺りは静寂に包まれている…</t>
+          <t>見慣れない木々がそびえ立っている。風一つ吹いていない静かな森だ。</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>cave_dragon</t>
+          <t>snowgrave</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>Alpha 14.1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ninho do Dragão</t>
+          <t>Permafrost</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Dragon's Nest</t>
+          <t>Permafrost</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>竜窟</t>
+          <t>永久凍土</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Isso é... o fim do mundo?</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Is this... the end of the world?</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>ここは…世界の果てだろうか？</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>underground</t>
+          <t>lumiest_graveyard</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3331,24 +3331,39 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Subterrâneo</t>
+          <t>O Cemitério</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Underground</t>
+          <t>The Graveyard</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>地下</t>
+          <t>墓所</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Você vê o cemitério de Lumiest. É silencioso. Muito silencioso.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>You see the graveyard of Lumiest. It's slient. Very silent.</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>墓所が見える。辺りは静寂に包まれている…</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>nymelle_crystal</t>
+          <t>cave_dragon</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3358,24 +3373,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Nymelle</t>
+          <t>Ninho do Dragão</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Nymelle</t>
+          <t>Dragon's Nest</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ナイミール</t>
+          <t>竜窟</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>nymelle_boss</t>
+          <t>underground</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3385,24 +3400,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Nymelle</t>
+          <t>Subsolo</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Nymelle</t>
+          <t>Underground</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ナイミール</t>
+          <t>地下</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>tent1</t>
+          <t>nymelle_crystal</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3412,516 +3427,570 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tenda</t>
+          <t>Nymelle</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tent</t>
+          <t>Nymelle</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>テント</t>
+          <t>ナイミール</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>tent2</t>
+          <t>nymelle_boss</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Beta 22.42</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tenda</t>
+          <t>Nymelle</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tent</t>
+          <t>Nymelle</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>テント</t>
+          <t>ナイミール</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>tent_snow</t>
+          <t>tent1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EA 23.145</t>
+          <t>Alpha 11.1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Iglu</t>
+          <t>Tenda</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Igloo</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>かまくら</t>
+          <t>テント</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>arena</t>
+          <t>tent2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Alpha 20.7</t>
+          <t>Beta 22.42</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Arena</t>
+          <t>Tenda</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Arena</t>
+          <t>Tent</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>闘技場</t>
+          <t>テント</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>instance_arena</t>
+          <t>tent_snow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Alpha 21.0</t>
+          <t>EA 23.145</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Campo de Batalha</t>
+          <t>Iglu</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Battlefield</t>
+          <t>Igloo</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>戦場</t>
+          <t>かまくら</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>instance_arena2</t>
+          <t>arena</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Alpha 21.0</t>
+          <t>Alpha 20.7</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Covil do Monstro</t>
+          <t>Arena</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Monster's Den</t>
+          <t>Arena</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>魔物の巣窟</t>
+          <t>闘技場</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>instance_harvest</t>
+          <t>instance_arena</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Alpha 21.6</t>
+          <t>Alpha 21.0</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Campo Suburbano</t>
+          <t>Campo de Batalha</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Suburban Field</t>
+          <t>Battlefield</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>郊外の畑</t>
+          <t>戦場</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>instance_music</t>
+          <t>instance_arena2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Alpha 21.6</t>
+          <t>Alpha 21.0</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sala de Concertos (Shows)</t>
+          <t>Covil de Monstros</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Concert Hall</t>
+          <t>Monster's Den</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>演奏会場</t>
+          <t>魔物の巣窟</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>instance_wedding</t>
+          <t>instance_harvest</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EA 23.278</t>
+          <t>Alpha 21.6</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Igreja Antiga</t>
+          <t>Campo Suburbano</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Old Church</t>
+          <t>Suburban Field</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>古い教会</t>
+          <t>郊外の畑</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>dungeon</t>
+          <t>instance_music</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Alpha 15.1</t>
+          <t>Alpha 21.6</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Caverna</t>
+          <t>Salão de Concertos</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Cave</t>
+          <t>Concert Hall</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>洞窟</t>
+          <t>演奏会場</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>gathering_plain</t>
+          <t>instance_wedding</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EA 23.99 Patch 1</t>
+          <t>EA 23.278</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ponto de Encontro</t>
+          <t>Igreja Velha</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Gathering Spot</t>
+          <t>Old Church</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>採取地</t>
+          <t>古い教会</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>dungeon_plain</t>
+          <t>dungeon</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EA 23.99 Patch 1</t>
+          <t>Alpha 15.1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Campos de Plantação</t>
+          <t>Caverna</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Grassland</t>
+          <t>Cave</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>草原</t>
+          <t>洞窟</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>dungeon_forest</t>
+          <t>gathering_plain</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Alpha 15.1</t>
+          <t>EA 23.99 Patch 1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Ponto de Encontro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Gathering Spot</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>森</t>
+          <t>採取地</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>dungeon_ruin</t>
+          <t>dungeon_plain</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Alpha 15.1</t>
+          <t>EA 23.99 Patch 1</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ruína</t>
+          <t>Campos</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Ruin</t>
+          <t>Grassland</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>遺跡</t>
+          <t>草原</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>dungeon_water</t>
+          <t>dungeon_forest</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EA 23.133</t>
+          <t>Alpha 15.1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ruína Subaquática</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Underwater Ruin</t>
+          <t>Forest</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>海底遺跡</t>
+          <t>森</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>dungeon_factory</t>
+          <t>dungeon_ruin</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EA 23.46</t>
+          <t>Alpha 15.1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ruínas de Máquinas</t>
+          <t>Ruínas</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Machinarium</t>
+          <t>Ruin</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>機械遺跡</t>
+          <t>遺跡</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>mine</t>
+          <t>dungeon_water</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.133</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Mina</t>
+          <t>Ruínas Submersas</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Mine</t>
+          <t>Underwater Ruin</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>鉱山</t>
+          <t>海底遺跡</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>cave_monster</t>
+          <t>dungeon_factory</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Alpha 17.1</t>
+          <t>EA 23.46</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Caverna do Monstro</t>
+          <t>Machinarium</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Monster Cave</t>
+          <t>Machinarium</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>魔物の巣窟</t>
+          <t>機械遺跡</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>mine</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Alpha 11.1</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Mina</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Mine</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>鉱山</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>cave_monster</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Alpha 17.1</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Caverna de Monstros</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Monster Cave</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>魔物の巣窟</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>asylum</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>EA 23.21</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>Orfanato</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>Orphanage</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>孤児院</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>Você vê um orfanato. As risadas das crianças ecoam no ar.</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Você vê um orfanato. O riso das crianças ecoa no ar.</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
         <is>
           <t>You see an orphanage. The laughter of children echoes in the air.</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>孤児院が見える。子供たちの笑い声が聞こえる。</t>
         </is>
